--- a/docs/ecpk/Оценка_ИТ-продукта_Битрикс24_ЕЦПК.xlsx
+++ b/docs/ecpk/Оценка_ИТ-продукта_Битрикс24_ЕЦПК.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="29" min="1" max="1"/>
@@ -600,7 +600,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -658,7 +657,7 @@
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>Официальное контейнерное окружение bitrix-tools/env-docker оркестрируется Docker Compose, а не Kubernetes. Готовых Helm Charts / манифестов K8s в репозитории нет. Контейнеризация приложения доступна на уровне Docker.</t>
+          <t>Официальное контейнерное окружение bitrix-tools/env-docker оркестрируется Docker Compose, а не Kubernetes. Готовых Helm Charts / манифестов K8s в репозитории нет. Контейнеризация приложения доступна на уровне Docker. Роль Transformer (Document Converter) контейнеризацию не поддерживает и не выделяется из PHP/app-ноды.</t>
         </is>
       </c>
       <c r="E5" s="19" t="n"/>
@@ -1087,21 +1086,36 @@
       </c>
     </row>
     <row r="24" ht="25.5" customHeight="1" s="29">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>* - указываются поддерживаемые версии (например, 12 и выше)</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>Transformer (конвертация документов)</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>модули transformer + transformercontroller (редакция Энтерпрайз)</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>Контейнеризация не поддерживается</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>Роль Document Converter / Transformer. Состав ОС-стека: erlang, rabbitmq-server, libreoffice-headless, ffmpeg; прикладные модули Битрикс24 — transformer и transformercontroller. В bitrix-tools/env-docker отдельного контейнера нет. Не может работать отдельно от PHP: ставится только на app-ноду вместе с PHP-FPM (обработка очереди и вызов конвертеров идут из PHP-контекста портала). Ограничение вендора: не более одной ноды с Transformer.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="25.5" customHeight="1" s="29">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>** - может ли решение работать как кластер в нескольких контейнерах (или только в одном)</t>
+          <t>* - указываются поддерживаемые версии (например, 12 и выше)</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
@@ -1111,7 +1125,11 @@
       <c r="F25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n"/>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>** - может ли решение работать как кластер в нескольких контейнерах (или только в одном)</t>
+        </is>
+      </c>
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="3" t="n"/>
@@ -1119,11 +1137,7 @@
       <c r="F26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Пример заполнения</t>
-        </is>
-      </c>
+      <c r="A27" s="1" t="n"/>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="3" t="n"/>
@@ -1131,57 +1145,41 @@
       <c r="F27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Пример заполнения</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Компонент</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Версия*</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Возможность контейнеризации**</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Поддержка компонента вендором</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Комментарий (описание назначения компонента)</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>PostgreSQL</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="inlineStr">
-        <is>
-          <t>12 и выше</t>
-        </is>
-      </c>
-      <c r="C29" s="31" t="inlineStr">
-        <is>
-          <t>Может работать как кластер в нескольких контейнерах</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>СУБД</t>
         </is>
       </c>
       <c r="F29" s="3" t="n"/>
@@ -1189,52 +1187,80 @@
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
-          <t>Автодокументы</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>12 и выше</t>
         </is>
       </c>
       <c r="C30" s="31" t="inlineStr">
         <is>
-          <t>Работает в одном контейнере</t>
+          <t>Может работать как кластер в нескольких контейнерах</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>Прикладное ПО, собственная разработка, конструктор выходных форм (шаблонов документов)</t>
-        </is>
-      </c>
+          <t>СУБД</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
         <is>
+          <t>Автодокументы</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Работает в одном контейнере</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>Прикладное ПО, собственная разработка, конструктор выходных форм (шаблонов документов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Keycloak </t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>21.5</t>
         </is>
       </c>
-      <c r="C31" s="31" t="inlineStr">
+      <c r="C32" s="31" t="inlineStr">
         <is>
           <t>Может работать как кластер в нескольких контейнерах</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>Инструмент идентификации пользователей</t>
         </is>
@@ -1260,7 +1286,7 @@
     <dataValidation sqref="C14:C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
       <formula1>Справочники!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation sqref="D14:D23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
+    <dataValidation sqref="D14:D24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
       <formula1>Справочники!$G$2:$G$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -1275,7 +1301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36.28515625" customWidth="1" style="29" min="1" max="3"/>
@@ -1500,90 +1526,6 @@
       <c r="D12" s="15" t="n"/>
       <c r="E12" s="15" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/docs/ecpk/Оценка_ИТ-продукта_Битрикс24_ЕЦПК.xlsx
+++ b/docs/ecpk/Оценка_ИТ-продукта_Битрикс24_ЕЦПК.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="29" min="1" max="1"/>
@@ -652,12 +652,12 @@
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Kubernetes не поддерживается</t>
+          <t>1.28 и выше</t>
         </is>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>Официальное контейнерное окружение bitrix-tools/env-docker оркестрируется Docker Compose, а не Kubernetes. Готовых Helm Charts / манифестов K8s в репозитории нет. Контейнеризация приложения доступна на уровне Docker. Роль Transformer (Document Converter) контейнеризацию не поддерживает и не выделяется из PHP/app-ноды.</t>
+          <t>Helm-чарт Yandex Cloud bitrix-env 1.0.6 (appVersion 9.0.10) явно задаёт kubeVersion &gt;=1.28.0-0. Официальный bitrix-tools/env-docker использует Docker Compose и сам по себе Kubernetes-манифестов не содержит.</t>
         </is>
       </c>
       <c r="E5" s="19" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
-          <t>Основные образы Bitrix24 (php, nginx, push, sphinx, ssl, lego) и redis/memcached — на базе Alpine. Образ СУБД quay.io/bitrix24/percona-server — на базе RHEL. Источник: https://github.com/bitrix-tools/env-docker/</t>
+          <t>Основные Bitrix-образы в bitrix-tools/env-docker собраны на Alpine; Percona Server — на базе RHEL, PostgreSQL — Debian. Helm-чарт использует образы Yandex Cloud/Bitrix и сторонние образы; базовую ОС каждого стороннего образа необходимо подтверждать по его SBOM/manifest перед аттестацией.</t>
         </is>
       </c>
       <c r="E6" s="19" t="n"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>Описание сервисов — docker-compose.yml и README репозитория env-docker; дополнительно см. docs/ecpk/описание_контейнеров_Битрикс24.md</t>
+          <t>Описание Docker Compose: bitrix-tools/env-docker и docs/ecpk/описание_контейнеров_Битрикс24.md. Описание Kubernetes: распакованный Helm-чарт charts/bitrix-env/.</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>В портале 1С-Битрикс24 (коробка) — модуль облачных хранилищ (clouds / main cloud storage) с провайдером Amazon S3 и совместимыми S3 API хранилищами (Yandex Object Storage, MinIO и др.). В env-docker по умолчанию используются Docker Volumes (файловая система); S3 подключается на уровне продукта.</t>
+          <t>Yandex Object Storage, вендор Yandex Cloud, S3 API; endpoint https://storage.yandexcloud.net, регион ru-central1. В Helm-чарте общие каталоги upload и backup подключаются через StorageClass csi-s3. Облачный сервис не имеет фиксированной версии продукта.</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
@@ -753,12 +753,13 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>Наличие манифеста в другом формате</t>
+          <t xml:space="preserve">Наличие Helm Charts 
+</t>
         </is>
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
-          <t>Формат манифеста: Docker Compose (docker-compose.yml). Helm Charts в официальном env-docker отсутствуют.</t>
+          <t>Helm-чарт Yandex Cloud bitrix-env версии 1.0.6, appVersion 9.0.10, Kubernetes &gt;=1.28.0-0; исходный OCI: oci://cr.yandex/yc-marketplace/yandex-cloud/bitrix-env/chart/bitrix-env. Дополнительно официальный env-docker предоставляет docker-compose.yml.</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
@@ -818,12 +819,12 @@
     <row r="14" ht="15" customHeight="1" s="29">
       <c r="A14" s="28" t="inlineStr">
         <is>
-          <t>1С-Битрикс24 (портал) / PHP-FPM</t>
+          <t>1С-Битрикс24 / PHP-FPM</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>8.2 и выше (в env-docker: 8.2.x; доступны 8.3.x, 8.4.x, 8.5.x)</t>
+          <t>8.2.30, 8.3.30, 8.4.19</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
@@ -838,7 +839,7 @@
       </c>
       <c r="E14" s="28" t="inlineStr">
         <is>
-          <t>Прикладное ПО вендора 1С-Битрикс; образ quay.io/bitrix24/php. Масштабирование web-нод при модуле «Веб-кластер».</t>
+          <t>Прикладное ПО. Основной Deployment Helm-чарта; replicaCount настраивается для prod-окружения.</t>
         </is>
       </c>
     </row>
@@ -850,7 +851,7 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>1.30.x и выше (образ quay.io/bitrix24/nginx)</t>
+          <t>1.28.3-v1</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -865,19 +866,19 @@
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>Веб-сервер / reverse proxy перед PHP-FPM. Сторонний компонент; Bitrix публикует подготовленный образ.</t>
+          <t>Веб-сервер в основном Deployment, масштабируется вместе с PHP-подами.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="28" t="inlineStr">
         <is>
-          <t>Percona Server (MySQL)</t>
+          <t>MySQL / Percona Server (внешняя СУБД)</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>8.0 и выше (в env-docker: 8.0.x; доступна 8.4.x)</t>
+          <t>8.0 и выше</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
@@ -892,19 +893,19 @@
       </c>
       <c r="E16" s="28" t="inlineStr">
         <is>
-          <t>Основная СУБД портала. Образ quay.io/bitrix24/percona-server. Кластер — через репликацию master/slave.</t>
+          <t>Основная СУБД портала. Helm-чарт СУБД не разворачивает: требуется внешний MySQL-совместимый сервис/кластер.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1" s="29">
       <c r="A17" s="28" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Redis</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>14 и выше (в env-docker по умолчанию 16.x)</t>
+          <t>8.6.2</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
@@ -919,19 +920,19 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>Опциональная СУБД в env-docker (для сценариев, где поддерживается PostgreSQL).</t>
+          <t>Опциональное хранилище кеша. Разворачивается зависимым Helm-чартом Redis/StatefulSet.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="32" t="inlineStr">
         <is>
-          <t>Redis</t>
+          <t>Push Server Битрикс24</t>
         </is>
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>7.2 и выше (в env-docker: 8.2.x)</t>
+          <t>3.2-v1</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -941,24 +942,24 @@
       </c>
       <c r="D18" s="32" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="E18" s="32" t="inlineStr">
         <is>
-          <t>Кеш, сессии, брокер для Push-сервера. Образ redis:*-alpine.</t>
+          <t>Очереди и real-time уведомления; отдельный Deployment, replicaCount настраивается.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>Memcached</t>
+          <t>Sphinx</t>
         </is>
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>1.6.x</t>
+          <t>2.2.11-v2</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -973,19 +974,19 @@
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>Альтернативное хранилище кеша (в т.ч. через модуль «Веб-кластер»). Образ memcached:*-alpine.</t>
+          <t>Полнотекстовый поиск; отдельный Deployment, replicaCount настраивается.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
         <is>
-          <t>Push-сервер Битрикс24</t>
+          <t>PHP-FPM Exporter</t>
         </is>
       </c>
       <c r="B20" s="32" t="inlineStr">
         <is>
-          <t>3.3 и выше</t>
+          <t>2.2.0</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -995,29 +996,29 @@
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="E20" s="32" t="inlineStr">
         <is>
-          <t>Собственный компонент вендора (образы push-pub / push-sub: quay.io/bitrix24/push). Real-time уведомления.</t>
+          <t>Опциональный экспорт метрик PHP; масштабируется вместе с основным Deployment.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t>Sphinx</t>
+          <t>Nginx Prometheus Exporter</t>
         </is>
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>2.2.11</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
-          <t>Работает в одном контейнере</t>
+          <t>Может работать как кластер в нескольких контейнерах</t>
         </is>
       </c>
       <c r="D21" s="32" t="inlineStr">
@@ -1027,7 +1028,7 @@
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>Полнотекстовый поиск. Образ quay.io/bitrix24/sphinx.</t>
+          <t>Опциональный экспорт метрик Nginx; масштабируется вместе с основным Deployment.</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1040,7 @@
       </c>
       <c r="B22" s="32" t="inlineStr">
         <is>
-          <t>PHP 8.2 и выше (тот же образ, что php)</t>
+          <t>образ PHP 8.2.30 / 8.3.30 / 8.4.19</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -1054,24 +1055,24 @@
       </c>
       <c r="E22" s="32" t="inlineStr">
         <is>
-          <t>Выполнение агентов/cron портала в отдельном контейнере на образе quay.io/bitrix24/php.</t>
+          <t>Выполнение агентов и резервного копирования по расписанию Kubernetes CronJob.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="25.5" customHeight="1" s="29">
       <c r="A23" s="32" t="inlineStr">
         <is>
-          <t>Lego / SSL</t>
+          <t>CSI-S3</t>
         </is>
       </c>
       <c r="B23" s="32" t="inlineStr">
         <is>
-          <t>Lego 4.35.x (ssl 1.2.x)</t>
+          <t>внешний компонент; версия чартом не закреплена</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
         <is>
-          <t>Работает в одном контейнере</t>
+          <t>Может работать как кластер в нескольких контейнерах</t>
         </is>
       </c>
       <c r="D23" s="32" t="inlineStr">
@@ -1081,53 +1082,68 @@
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Вспомогательные контейнеры выпуска и хранения TLS-сертификатов (Let’s Encrypt / self-signed).</t>
+          <t>StorageClass csi-s3 для подключения Yandex Object Storage к каталогам upload и backup.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="25.5" customHeight="1" s="29">
       <c r="A24" s="32" t="inlineStr">
         <is>
+          <t>cert-manager</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>внешний компонент; версия чартом не закреплена</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>Может работать как кластер в нескольких контейнерах</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>Опциональный выпуск TLS-сертификатов; вместо него можно передать существующий Kubernetes Secret.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25.5" customHeight="1" s="29">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
           <t>Transformer (конвертация документов)</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
-        <is>
-          <t>модули transformer + transformercontroller (редакция Энтерпрайз)</t>
-        </is>
-      </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>transformer и transformercontroller 20.100.0 и выше (Энтерпрайз)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
         <is>
           <t>Контейнеризация не поддерживается</t>
         </is>
       </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="D25" s="32" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr">
-        <is>
-          <t>Роль Document Converter / Transformer. Состав ОС-стека: erlang, rabbitmq-server, libreoffice-headless, ffmpeg; прикладные модули Битрикс24 — transformer и transformercontroller. В bitrix-tools/env-docker отдельного контейнера нет. Не может работать отдельно от PHP: ставится только на app-ноду вместе с PHP-FPM (обработка очереди и вызов конвертеров идут из PHP-контекста портала). Ограничение вендора: не более одной ноды с Transformer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="25.5" customHeight="1" s="29">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>* - указываются поддерживаемые версии (например, 12 и выше)</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>Отдельного образа в env-docker и Helm-чарте нет. Состав: модули transformer/transformercontroller, Erlang, RabbitMQ Server, LibreOffice, FFmpeg. Серверная роль требует PHP и сайт Битрикс с transformercontroller; автономно без PHP не работает, но может по HTTP обслуживать другие сайты. Одна роль на машину.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>** - может ли решение работать как кластер в нескольких контейнерах (или только в одном)</t>
+          <t>* - указываются поддерживаемые версии (например, 12 и выше)</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -1137,7 +1153,11 @@
       <c r="F26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n"/>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>** - может ли решение работать как кластер в нескольких контейнерах (или только в одном)</t>
+        </is>
+      </c>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="3" t="n"/>
@@ -1145,11 +1165,7 @@
       <c r="F27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Пример заполнения</t>
-        </is>
-      </c>
+      <c r="A28" s="1" t="n"/>
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="3" t="n"/>
@@ -1157,57 +1173,41 @@
       <c r="F28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Пример заполнения</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Компонент</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Версия*</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Возможность контейнеризации**</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Поддержка компонента вендором</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Комментарий (описание назначения компонента)</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>PostgreSQL</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>12 и выше</t>
-        </is>
-      </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>Может работать как кластер в нескольких контейнерах</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>СУБД</t>
         </is>
       </c>
       <c r="F30" s="3" t="n"/>
@@ -1215,52 +1215,80 @@
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
         <is>
-          <t>Автодокументы</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>12 и выше</t>
         </is>
       </c>
       <c r="C31" s="31" t="inlineStr">
         <is>
-          <t>Работает в одном контейнере</t>
+          <t>Может работать как кластер в нескольких контейнерах</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>Прикладное ПО, собственная разработка, конструктор выходных форм (шаблонов документов)</t>
-        </is>
-      </c>
+          <t>СУБД</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
         <is>
+          <t>Автодокументы</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>Работает в одном контейнере</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>Прикладное ПО, собственная разработка, конструктор выходных форм (шаблонов документов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Keycloak </t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>21.5</t>
         </is>
       </c>
-      <c r="C32" s="31" t="inlineStr">
+      <c r="C33" s="31" t="inlineStr">
         <is>
           <t>Может работать как кластер в нескольких контейнерах</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>Инструмент идентификации пользователей</t>
         </is>
@@ -1269,7 +1297,7 @@
   </sheetData>
   <dataValidations count="7">
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
-      <formula1>Справочники!$A$2:$A$4</formula1>
+      <formula1>Справочники!$A$2:$A$5</formula1>
     </dataValidation>
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
       <formula1>Справочники!$B$2:$B$6</formula1>
@@ -1283,10 +1311,10 @@
     <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
       <formula1>Справочники!$E$2:$E$4</formula1>
     </dataValidation>
-    <dataValidation sqref="C14:C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
-      <formula1>Справочники!$F$2:$F$3</formula1>
+    <dataValidation sqref="C14:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
+      <formula1>Справочники!$F$2:$F$4</formula1>
     </dataValidation>
-    <dataValidation sqref="D14:D24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
+    <dataValidation sqref="D14:D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
       <formula1>Справочники!$G$2:$G$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -1445,10 +1473,18 @@
           <t>Отсутствие манифеста</t>
         </is>
       </c>
-      <c r="F4" s="15" t="n"/>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Контейнеризация не поддерживается</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>1.28 и выше</t>
+        </is>
+      </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ubuntu </t>
